--- a/Data/UserData.xlsx
+++ b/Data/UserData.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="8">
   <si>
     <t>email</t>
   </si>
@@ -37,13 +37,14 @@
     <t>test@mail.com</t>
   </si>
   <si>
-    <t>TC Status</t>
+    <t>PASS</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="3">
     <font>
       <sz val="11"/>
@@ -401,9 +402,9 @@
   <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="15.7109375" customWidth="1"/>
-    <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="15.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="12.0"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="19.28515625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -416,9 +417,7 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>7</v>
-      </c>
+      <c r="D1" s="1"/>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="3" t="s">
@@ -430,6 +429,9 @@
       <c r="C2" s="2" t="s">
         <v>5</v>
       </c>
+      <c r="D2" t="s" s="0">
+        <v>7</v>
+      </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="3" t="s">
@@ -440,6 +442,9 @@
       </c>
       <c r="C3" s="2" t="s">
         <v>5</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
